--- a/work/data/leaderboard_text.xlsx
+++ b/work/data/leaderboard_text.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>claude-fable-5</t>
+          <t>claude-fable-5-high</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">

--- a/work/data/leaderboard_text.xlsx
+++ b/work/data/leaderboard_text.xlsx
@@ -540,11 +540,11 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>claude-fable-5-high</t>
+          <t>claude-opus-5.5-high</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1506</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="3" ht="11" customHeight="1">
@@ -570,26 +570,26 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>claude-fable-5-high</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="5" ht="11" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
           <t>claude-opus-4-7-high</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C5" s="4" t="n">
         <v>1502</v>
-      </c>
-    </row>
-    <row r="5" ht="11" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>muse-spark-1.2 (xHigh)</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>1500</v>
       </c>
     </row>
     <row r="6" ht="11" customHeight="1">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1498</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="7" ht="11" customHeight="1">
@@ -619,97 +619,97 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="8" ht="11" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>muse-spark-1.2 (xHigh)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="9" ht="11" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
           <t>claude-opus-4-7</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C9" s="4" t="n">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="10" ht="11" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>muse-spark-1.3-max</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>1494</v>
       </c>
     </row>
-    <row r="9" ht="11" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>muse-spark-1.3-max</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>1493</v>
-      </c>
-    </row>
-    <row r="10" ht="11" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+    <row r="11" ht="11" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>gemini-3.8-flash-high</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>1493</v>
-      </c>
-    </row>
-    <row r="11" ht="11" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="n">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="12" ht="11" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>claude-opus-5-high</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>1493</v>
-      </c>
-    </row>
-    <row r="12" ht="11" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="n">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="13" ht="11" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>muse-spark-1.1</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>1493</v>
-      </c>
-    </row>
-    <row r="13" ht="11" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>gemini-3.7-flash-high</t>
-        </is>
-      </c>
       <c r="C13" s="4" t="n">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="1">
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="1">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="1">
@@ -750,67 +750,67 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>gemini-3.7-flash-high</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="17" ht="11" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>kimi-k3-max</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="18" ht="11" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
           <t>gemini-3.1-pro-preview</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C18" s="4" t="n">
         <v>1487</v>
       </c>
     </row>
-    <row r="17" ht="11" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+    <row r="19" ht="11" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>gemini-3-pro</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C19" s="4" t="n">
         <v>1485</v>
       </c>
     </row>
-    <row r="18" ht="11" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>kimi-k3-max</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>1485</v>
-      </c>
-    </row>
-    <row r="19" ht="11" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
+    <row r="20" ht="11" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>gpt-5.6-sol-xhigh</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>1483</v>
-      </c>
-    </row>
-    <row r="20" ht="11" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>glm-5.3-max</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
@@ -818,14 +818,14 @@
       </c>
     </row>
     <row r="21" ht="11" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>gpt-5.5-high</t>
+          <t>gemini-3.6-flash-high</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
@@ -833,14 +833,14 @@
       </c>
     </row>
     <row r="22" ht="11" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-4-8-high</t>
+          <t>gpt-5.5-high</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
@@ -848,29 +848,29 @@
       </c>
     </row>
     <row r="23" ht="11" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>qwen3.8-max</t>
+          <t>claude-opus-4-8-high</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>gemini-3.6-flash-high</t>
+          <t>mimo-v2.6-pro</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
@@ -878,14 +878,14 @@
       </c>
     </row>
     <row r="25" ht="11" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>gpt-6-astra-max</t>
+          <t>glm-5.3-max</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
@@ -893,18 +893,18 @@
       </c>
     </row>
     <row r="26" ht="11" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>gemini-3.5-flash-high</t>
+          <t>qwen3.8-max</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1478</v>
+        <v>1479</v>
       </c>
     </row>
   </sheetData>

--- a/work/data/leaderboard_text.xlsx
+++ b/work/data/leaderboard_text.xlsx
@@ -32,7 +32,7 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="004472C4"/>
+      <color rgb="00FF0000"/>
       <sz val="8"/>
     </font>
     <font>
@@ -47,12 +47,12 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00D9D9D9"/>
+      <color rgb="004472C4"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00FF0000"/>
+      <color rgb="00D9D9D9"/>
       <sz val="8"/>
     </font>
     <font>
@@ -75,6 +75,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+        <bgColor rgb="00FF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
       </patternFill>
@@ -83,12 +89,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9D9D9"/>
         <bgColor rgb="00D9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF0000"/>
-        <bgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -540,15 +540,15 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-5.5-high</t>
+          <t>gemini-4-argon-high</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1509</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="3" ht="11" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>■</t>
         </is>
@@ -563,7 +563,7 @@
       </c>
     </row>
     <row r="4" ht="11" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>■</t>
         </is>
@@ -574,52 +574,52 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="5" ht="11" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>claude-opus-5.5-high</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>1504</v>
       </c>
     </row>
-    <row r="5" ht="11" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+    <row r="6" ht="11" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>claude-opus-4-7-high</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C6" s="4" t="n">
         <v>1502</v>
       </c>
     </row>
-    <row r="6" ht="11" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+    <row r="7" ht="11" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>claude-fable-5.1-max</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C7" s="4" t="n">
         <v>1501</v>
-      </c>
-    </row>
-    <row r="7" ht="11" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>claude-opus-4-6</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>1498</v>
       </c>
     </row>
     <row r="8" ht="11" customHeight="1">
@@ -630,22 +630,22 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>muse-spark-1.2 (xHigh)</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="9" ht="11" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-4-7</t>
+          <t>muse-spark-1.3-max</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
@@ -660,7 +660,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>muse-spark-1.3-max</t>
+          <t>claude-opus-4-7</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
@@ -675,11 +675,11 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>gemini-3.8-flash-high</t>
+          <t>muse-spark-1.2 (xHigh)</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1492</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="1">
@@ -690,15 +690,15 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-5-high</t>
+          <t>gemini-3.8-flash-high</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1491</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="1">
@@ -720,26 +720,26 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>muse-spark</t>
+          <t>claude-opus-5-high</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="15" ht="11" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>claude-opus-5-max</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
         <v>1489</v>
-      </c>
-    </row>
-    <row r="15" ht="11" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>claude-opus-5-max</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>1488</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="1">
@@ -750,22 +750,22 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>muse-spark</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="17" ht="11" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
           <t>gemini-3.7-flash-high</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>1488</v>
-      </c>
-    </row>
-    <row r="17" ht="11" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>kimi-k3-max</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
@@ -773,93 +773,93 @@
       </c>
     </row>
     <row r="18" ht="11" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>kimi-k3-max</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="19" ht="11" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>gemini-3.1-pro-preview</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C19" s="4" t="n">
         <v>1487</v>
       </c>
     </row>
-    <row r="19" ht="11" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
+    <row r="20" ht="11" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>gemini-3-pro</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C20" s="4" t="n">
         <v>1485</v>
       </c>
     </row>
-    <row r="20" ht="11" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
+    <row r="21" ht="11" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>gpt-5.6-sol-xhigh</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C21" s="4" t="n">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="22" ht="11" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>gemini-3.6-flash-high</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
         <v>1483</v>
       </c>
     </row>
-    <row r="21" ht="11" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>gemini-3.6-flash-high</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>1482</v>
-      </c>
-    </row>
-    <row r="22" ht="11" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
+    <row r="23" ht="11" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>gpt-5.5-high</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C23" s="4" t="n">
         <v>1481</v>
-      </c>
-    </row>
-    <row r="23" ht="11" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>claude-opus-4-8-high</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>1480</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="1">
@@ -870,11 +870,11 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>mimo-v2.6-pro</t>
+          <t>claude-opus-4-8-high</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="1">
@@ -885,26 +885,26 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>glm-5.3-max</t>
+          <t>qwen3.8-max</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="26" ht="11" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>mimo-v2.6-pro</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
         <v>1480</v>
-      </c>
-    </row>
-    <row r="26" ht="11" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>qwen3.8-max</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>1479</v>
       </c>
     </row>
   </sheetData>

--- a/work/data/leaderboard_text.xlsx
+++ b/work/data/leaderboard_text.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="5" ht="11" customHeight="1">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="7" ht="11" customHeight="1">
@@ -638,14 +638,14 @@
       </c>
     </row>
     <row r="9" ht="11" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>muse-spark-1.3-max</t>
+          <t>gemini-3.8-flash-high</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
@@ -653,14 +653,14 @@
       </c>
     </row>
     <row r="10" ht="11" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-4-7</t>
+          <t>muse-spark-1.3-max</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
@@ -668,14 +668,14 @@
       </c>
     </row>
     <row r="11" ht="11" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>muse-spark-1.2 (xHigh)</t>
+          <t>claude-opus-4-7</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
@@ -683,14 +683,14 @@
       </c>
     </row>
     <row r="12" ht="11" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>gemini-3.8-flash-high</t>
+          <t>muse-spark-1.2 (xHigh)</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="1">
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1491</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="1">
@@ -758,14 +758,14 @@
       </c>
     </row>
     <row r="17" ht="11" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>gemini-3.7-flash-high</t>
+          <t>kimi-k3-max</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
@@ -773,14 +773,14 @@
       </c>
     </row>
     <row r="18" ht="11" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>kimi-k3-max</t>
+          <t>gemini-3.7-flash-high</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
@@ -833,14 +833,14 @@
       </c>
     </row>
     <row r="22" ht="11" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>gemini-3.6-flash-high</t>
+          <t>gpt-6.1-sol-max</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
@@ -848,63 +848,63 @@
       </c>
     </row>
     <row r="23" ht="11" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
+          <t>gemini-3.6-flash-high</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="24" ht="11" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>qwen3.8-max</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="25" ht="11" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8-high</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="26" ht="11" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
           <t>gpt-5.5-high</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C26" s="4" t="n">
         <v>1481</v>
-      </c>
-    </row>
-    <row r="24" ht="11" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>claude-opus-4-8-high</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>1481</v>
-      </c>
-    </row>
-    <row r="25" ht="11" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>qwen3.8-max</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>1481</v>
-      </c>
-    </row>
-    <row r="26" ht="11" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>mimo-v2.6-pro</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>1480</v>
       </c>
     </row>
   </sheetData>

--- a/work/data/leaderboard_text.xlsx
+++ b/work/data/leaderboard_text.xlsx
@@ -555,11 +555,11 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-high</t>
+          <t>claude-opus-5.5-high</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1505</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="4" ht="11" customHeight="1">
@@ -570,7 +570,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>claude-fable-5-high</t>
+          <t>claude-opus-4-6-high</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
@@ -585,7 +585,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-5.5-high</t>
+          <t>claude-fable-5-high</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="9" ht="11" customHeight="1">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1495</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="10" ht="11" customHeight="1">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1494</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="1">
@@ -780,11 +780,11 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>gemini-3.7-flash-high</t>
+          <t>gemini-3.1-pro-preview</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="1">
@@ -795,11 +795,11 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>gemini-3.1-pro-preview</t>
+          <t>gemini-3.7-flash-high</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="1">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="1">
@@ -844,18 +844,18 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>gemini-3.6-flash-high</t>
+          <t>qwen3.8-max</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
@@ -863,14 +863,14 @@
       </c>
     </row>
     <row r="24" ht="11" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>qwen3.8-max</t>
+          <t>gemini-3.6-flash-high</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
@@ -878,14 +878,14 @@
       </c>
     </row>
     <row r="25" ht="11" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-4-8-high</t>
+          <t>gpt-5.5-high</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
@@ -893,14 +893,14 @@
       </c>
     </row>
     <row r="26" ht="11" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>gpt-5.5-high</t>
+          <t>claude-opus-4-8-high</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">

--- a/work/data/leaderboard_text.xlsx
+++ b/work/data/leaderboard_text.xlsx
@@ -47,12 +47,12 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="004472C4"/>
+      <color rgb="00D9D9D9"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00D9D9D9"/>
+      <color rgb="004472C4"/>
       <sz val="8"/>
     </font>
     <font>
@@ -81,14 +81,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-        <bgColor rgb="00D9D9D9"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -555,67 +555,67 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>muse-wonder-max</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="4" ht="11" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>claude-opus-5.5-high</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>1507</v>
-      </c>
-    </row>
-    <row r="4" ht="11" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="n">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="5" ht="11" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>claude-fable-5-high</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="6" ht="11" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>claude-opus-4-6-high</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>1504</v>
-      </c>
-    </row>
-    <row r="5" ht="11" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>claude-fable-5-high</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>1504</v>
-      </c>
-    </row>
-    <row r="6" ht="11" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="n">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="7" ht="11" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>claude-opus-4-7-high</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>1501</v>
-      </c>
-    </row>
-    <row r="7" ht="11" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>claude-fable-5.1-max</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
@@ -623,48 +623,48 @@
       </c>
     </row>
     <row r="8" ht="11" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>claude-fable-5.1-max</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="9" ht="11" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C9" s="4" t="n">
         <v>1498</v>
       </c>
     </row>
-    <row r="9" ht="11" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+    <row r="10" ht="11" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>gemini-3.8-flash-high</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
-        <v>1497</v>
-      </c>
-    </row>
-    <row r="10" ht="11" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>muse-spark-1.3-max</t>
-        </is>
-      </c>
       <c r="C10" s="4" t="n">
-        <v>1494</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="11" ht="11" customHeight="1">
@@ -675,26 +675,26 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-4-7</t>
+          <t>muse-spark-1.2 (xHigh)</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="12" ht="11" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>muse-spark-1.3-max</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
         <v>1494</v>
-      </c>
-    </row>
-    <row r="12" ht="11" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>muse-spark-1.2 (xHigh)</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>1492</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="1">
@@ -705,11 +705,11 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>muse-spark-1.1</t>
+          <t>claude-opus-4-7</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1491</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="1">
@@ -720,7 +720,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-5-high</t>
+          <t>muse-spark-1.1</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
@@ -728,18 +728,18 @@
       </c>
     </row>
     <row r="15" ht="11" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-5-max</t>
+          <t>claude-opus-5-high</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="1">
@@ -750,41 +750,41 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>claude-opus-5-max</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="17" ht="11" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
           <t>muse-spark</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C17" s="4" t="n">
         <v>1489</v>
       </c>
     </row>
-    <row r="17" ht="11" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+    <row r="18" ht="11" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>kimi-k3-max</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C18" s="4" t="n">
         <v>1488</v>
-      </c>
-    </row>
-    <row r="18" ht="11" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>gemini-3.1-pro-preview</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>1487</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="1">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="1">
@@ -810,22 +810,22 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
+          <t>gemini-3.1-pro-preview</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="21" ht="11" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t>gemini-3-pro</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>1485</v>
-      </c>
-    </row>
-    <row r="21" ht="11" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>gpt-5.6-sol-xhigh</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
@@ -840,26 +840,26 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
+          <t>gpt-5.6-sol-xhigh</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="23" ht="11" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
           <t>gpt-6.1-sol-max</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C23" s="4" t="n">
         <v>1484</v>
-      </c>
-    </row>
-    <row r="23" ht="11" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>qwen3.8-max</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>1483</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="1">
@@ -874,18 +874,18 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>gpt-5.5-high</t>
+          <t>qwen3.8-max</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
@@ -893,7 +893,7 @@
       </c>
     </row>
     <row r="26" ht="11" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
   </sheetData>
